--- a/apps/shell/fixtures/basis-template-sample.xlsx
+++ b/apps/shell/fixtures/basis-template-sample.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E27"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -625,16 +625,16 @@
         <v/>
       </c>
       <c r="B14" t="str">
-        <v>Goodwill &amp; Intangibles</v>
+        <v>Other Current Assets</v>
       </c>
       <c r="C14">
-        <v>610</v>
+        <v>15</v>
       </c>
       <c r="D14">
-        <v>598</v>
+        <v>17</v>
       </c>
       <c r="E14">
-        <v>586</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -642,16 +642,16 @@
         <v/>
       </c>
       <c r="B15" t="str">
-        <v>Other Long Term Assets</v>
+        <v>Goodwill &amp; Intangibles</v>
       </c>
       <c r="C15">
-        <v>34</v>
+        <v>610</v>
       </c>
       <c r="D15">
-        <v>36</v>
+        <v>598</v>
       </c>
       <c r="E15">
-        <v>38</v>
+        <v>586</v>
       </c>
     </row>
     <row r="16">
@@ -659,16 +659,16 @@
         <v/>
       </c>
       <c r="B16" t="str">
-        <v>AP</v>
+        <v>Other Long Term Assets</v>
       </c>
       <c r="C16">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D16">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E16">
-        <v>27</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
@@ -676,16 +676,16 @@
         <v/>
       </c>
       <c r="B17" t="str">
-        <v>Unearned Revenue</v>
+        <v>AP</v>
       </c>
       <c r="C17">
-        <v>134</v>
+        <v>22</v>
       </c>
       <c r="D17">
-        <v>149</v>
+        <v>24</v>
       </c>
       <c r="E17">
-        <v>168</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18">
@@ -693,16 +693,16 @@
         <v/>
       </c>
       <c r="B18" t="str">
-        <v>Other Current Liabilities</v>
+        <v>Unearned Revenue</v>
       </c>
       <c r="C18">
-        <v>29</v>
+        <v>134</v>
       </c>
       <c r="D18">
-        <v>31</v>
+        <v>149</v>
       </c>
       <c r="E18">
-        <v>33</v>
+        <v>168</v>
       </c>
     </row>
     <row r="19">
@@ -710,33 +710,33 @@
         <v/>
       </c>
       <c r="B19" t="str">
-        <v>Total Borrowings</v>
+        <v>Other Current Liabilities</v>
       </c>
       <c r="C19">
-        <v>420</v>
+        <v>29</v>
       </c>
       <c r="D19">
-        <v>390</v>
+        <v>31</v>
       </c>
       <c r="E19">
-        <v>355</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Cash Flow Statement</v>
+        <v/>
       </c>
       <c r="B20" t="str">
-        <v>SBC</v>
+        <v>Total Borrowings</v>
       </c>
       <c r="C20">
-        <v>14</v>
+        <v>420</v>
       </c>
       <c r="D20">
-        <v>16</v>
+        <v>390</v>
       </c>
       <c r="E20">
-        <v>18</v>
+        <v>355</v>
       </c>
     </row>
     <row r="21">
@@ -744,33 +744,33 @@
         <v/>
       </c>
       <c r="B21" t="str">
-        <v>Capex</v>
+        <v>Other Long Term Liabilities</v>
       </c>
       <c r="C21">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D21">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E21">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>EBITDA</v>
+        <v>Cash Flow Statement</v>
       </c>
       <c r="B22" t="str">
-        <v>Restructuring &amp; Severance</v>
+        <v>SBC</v>
       </c>
       <c r="C22">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D22">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -778,33 +778,33 @@
         <v/>
       </c>
       <c r="B23" t="str">
-        <v>Transaction &amp; Integration Costs</v>
+        <v>Capex</v>
       </c>
       <c r="C23">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D23">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Working Capital</v>
+        <v>EBITDA</v>
       </c>
       <c r="B24" t="str">
-        <v>Days Sales Outstanding</v>
+        <v>Restructuring &amp; Severance</v>
       </c>
       <c r="C24">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="D24">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="E24">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -812,21 +812,55 @@
         <v/>
       </c>
       <c r="B25" t="str">
+        <v>Transaction &amp; Integration Costs</v>
+      </c>
+      <c r="C25">
+        <v>9</v>
+      </c>
+      <c r="D25">
+        <v>4</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Working Capital</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Days Sales Outstanding</v>
+      </c>
+      <c r="C26">
+        <v>41</v>
+      </c>
+      <c r="D26">
+        <v>42</v>
+      </c>
+      <c r="E26">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v/>
+      </c>
+      <c r="B27" t="str">
         <v>Days Payable Outstanding</v>
       </c>
-      <c r="C25">
+      <c r="C27">
         <v>28</v>
       </c>
-      <c r="D25">
+      <c r="D27">
         <v>28</v>
       </c>
-      <c r="E25">
+      <c r="E27">
         <v>29</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E27"/>
   </ignoredErrors>
 </worksheet>
 </file>